--- a/paper/source_data/fig3_source_data.xlsx
+++ b/paper/source_data/fig3_source_data.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One sheet per panel with exactly the plotted values, intervals, floored counts and labels. Each row names the aggregate file it was read from and that file's SHA-256.</t>
+          <t>One sheet per panel with exactly the plotted values, intervals, floored counts and labels. Each row names the aggregate file it was read from and that file's SHA-256, with one further column pair for each further file a row was read from.</t>
         </is>
       </c>
     </row>
@@ -496,12 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>**Fig. 3 | BRAN compared with foundation models given one or both modalities.** Detection of 26 conditions from the AI-READI medical history, six possibly defined from encoder inputs, in 1,928 development participants.
-**a**, Macro AUROC and BRAN minus each foundation model given one modality plus age (development, secondary analysis). Diamonds, official-test eye-alone contrasts.
-**b**, Macro AUROC as each foundation model gains the other modality.
-**c**, As in **a** for foundation models given both modalities, raw clinical values plus age and PCA-64 readouts. Ticks, one-sided Bonferroni bounds over five prespecified comparators. Lower block, the single scoring of a previously accessed official test (n ≥ 340, 24 conditions). Bottom, condition-group macro AUROC.
-**d**, Per-condition wins, ties and losses against eight foundation-model arms (unadjusted paired 95% intervals).
-Points, estimates. Bars, 95% participant bootstrap intervals (1,000 development and 2,000 official-test draws). †, tuned probe on the frozen BRAN state. ‡, BRAN's own condition heads. Adverse results. Every retinal foundation model beat BRAN's eye-only route in development, and VisionFM did so in the official test (**a**). Tuned BRAN combined tied its clinical-only route (**b**) and RETFound-Green, DINOv3, Labrador and raw clinical values plus age (**c**), and PCA-64 readouts tied the native heads. After Holm adjustment the native heads led raw clinical values plus age only in eye conditions, where RETFound-Green and DINOv3 with clinical data beat them, and trailed BRAN's clinical probe in cardiometabolic and vascular conditions (**c**). Official-test bounds cleared zero only for VisionFM (unadjusted one-sided P = 0.0005, others 0.036 to 0.4203, Bonferroni threshold 0.01), so **c** did not replicate, as prespecified power of 0.15 or less anticipated. Per-arm tuning removed the fixed C = 1 lead over three arms given both modalities (Extended Data Fig. 3c). Glaucoma and cataracts gave 9 of the 16 losses (**d**). VisionFM often chose the grid-edge C, so its estimates may be low. The **a** and **b** contrasts and **c** groups were specified after earlier results. RETFound-Green is not the original RETFound, and a Labrador cache discrepancy is unresolved. Only BRAN saw the 26 labels, and a label-free BRAN comparison is PLACEHOLDER.</t>
+          <t>**Fig. 3 | BRAN compared with foundation models given one or both modalities.** Twenty-six self-reported conditions (six possibly encoder-defined), 1,928 AI-READI development participants. **a**, BRAN against foundation models given one modality plus age (secondary). Diamonds, official test. **b**, Foundation models given the other modality. **c**, As in **a** with both modalities, raw clinical values and PCA-64 readouts. Ticks, one-sided Bonferroni bounds over five prespecified comparators. Lower block, single scoring of a previously accessed official test (*n* ≥ 340, 24 conditions). **d**, Per-condition wins, ties and losses against eight foundation-model arms (unadjusted paired 95% intervals). Bars, participant bootstrap 95% intervals (1,000 development, 2,000 test draws). †, tuned probe on the frozen state. ‡, native condition heads. Eye alone, every retinal foundation model beat BRAN in development, as did VisionFM (adjusted) and RETFound-Green (unadjusted) on the official test (**a**). Tuned BRAN combined tied its clinical route (**b**), RETFound-Green, DINOv3, Labrador and raw clinical values (**c**), and PCA-64 readouts tied the native heads. By condition group (Holm), native heads led raw clinical values only for eye conditions, where RETFound-Green and DINOv3 with clinical data beat them, and trailed the clinical probe for cardiometabolic and vascular conditions. Official-test bounds cleared zero only for VisionFM (one-sided *P* = 0.0005, others 0.036 to 0.4203, threshold 0.01), so **c** did not replicate, as prespecified power of 0.15 or less anticipated. Glaucoma and cataracts gave 9 of 16 losses (**d**). Panels **a**, **b** and the **c** groups were specified after earlier results. RETFound-Green is not the original RETFound, a Labrador cache discrepancy is unresolved, only BRAN saw the labels and a label-free comparison is PLACEHOLDER.</t>
         </is>
       </c>
     </row>
